--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -51,6 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE9828C"/>
         <bgColor/>
       </patternFill>
@@ -63,6 +69,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -81,37 +117,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,18 +183,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -147,55 +309,475 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE15462"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,49 +807,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,13 +825,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,12 +897,396 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -321,25 +1305,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,1063 +1395,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>002691</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -1601.84万</v>
       </c>
       <c r="E2">
@@ -4121,40 +4121,40 @@
       <c r="H2">
         <v>-2.71</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="6">
         <v>13.05</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <v>24.4</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="2">
         <v>36.85</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="8">
         <v>23.21</v>
       </c>
       <c r="M2" s="13">
         <v>30.98</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="9">
         <v>28.29</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="3">
         <v>29.48</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>25.4</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="12">
         <v>20.82</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="10">
         <v>8.76</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="4">
         <v>3.09</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="5">
         <v>-27.39</v>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,40 +4183,40 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="14">
         <v>5.22</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="22">
         <v>15.75</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="15">
         <v>4.21</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="16">
         <v>10.78</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="19">
         <v>8.51</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="23">
         <v>9.52</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="17">
         <v>6.07</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="25">
         <v>2.19</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="24">
         <v>-8</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="18">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="20">
         <v>-12.72</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="26">
         <v>-38.58</v>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>000856</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -799.12万</v>
       </c>
       <c r="E4">
@@ -4245,40 +4245,40 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="27">
         <v>15.18</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="36">
         <v>26.73</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>39.36</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="29">
         <v>53.27</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="32">
         <v>43.18</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="28">
         <v>29.45</v>
       </c>
       <c r="O4" s="30">
         <v>24.18</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="33">
         <v>23</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="34">
         <v>16.55</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="35">
         <v>16</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="38">
         <v>12</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="31">
         <v>-2.73</v>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,40 +4307,40 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="46">
         <v>16.27</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="51">
         <v>13.88</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="42">
         <v>14.94</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="43">
         <v>11.32</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="47">
         <v>7.25</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="48">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="52">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="40">
         <v>-8.4</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="44">
         <v>-11.23</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="49">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="50">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="45">
+      <c r="T5" s="41">
         <v>-35.54</v>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>600881</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -413.93万</v>
       </c>
       <c r="E6">
@@ -4369,40 +4369,40 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="65">
         <v>9.64</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="59">
         <v>13.71</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="53">
         <v>10.66</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="54">
         <v>7.11</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="55">
         <v>5.08</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="56">
         <v>6.09</v>
       </c>
       <c r="O6" s="60">
         <v>7.61</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="63">
         <v>3.55</v>
       </c>
       <c r="Q6" s="61">
         <v>5.08</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="57">
         <v>4.06</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="64">
         <v>7.61</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="58">
         <v>-20.3</v>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,40 +4431,40 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="78">
         <v>12.74</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="66">
         <v>35.28</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="73">
         <v>44.34</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="74">
         <v>37.24</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="68">
         <v>52.36</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="67">
         <v>52.32</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="69">
         <v>48.5</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="75">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="76">
         <v>66.56</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="70">
         <v>71.24</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="71">
         <v>61</v>
       </c>
-      <c r="T7" s="77">
+      <c r="T7" s="72">
         <v>60.57</v>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>301488</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="89" t="str">
         <v>净卖: -1455.69万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>8.31</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="90">
         <v>10.79</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="81">
         <v>18.2</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="91">
         <v>12.39</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="82">
         <v>24.77</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="83">
         <v>24.74</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="85">
         <v>21.61</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="86">
         <v>42.12</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="87">
         <v>36.4</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="84">
         <v>40.23</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="79">
         <v>31.84</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="80">
         <v>41.24</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="88">
         <v>31.5</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="94" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4555,37 +4555,37 @@
       <c r="H9">
         <v>2.53</v>
       </c>
-      <c r="I9" s="94">
+      <c r="I9" s="92">
         <v>7.31</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="97">
         <v>14.01</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="98">
         <v>11.84</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="100">
         <v>10.5</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="101">
         <v>4.53</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="99">
         <v>1.13</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="95">
         <v>3.09</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="102">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="103">
         <v>4.33</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="96">
         <v>3.3</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="104">
         <v>5.36</v>
       </c>
       <c r="T9" s="93">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>603595</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="108" t="str">
         <v>净买: 1022.73万</v>
       </c>
       <c r="E10">
@@ -4617,40 +4617,40 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="115">
         <v>6.97</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="117">
         <v>3.98</v>
       </c>
       <c r="K10" s="109">
         <v>-2.59</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="110">
         <v>-2.43</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="111">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="116">
         <v>-0.32</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="112">
         <v>3.94</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="106">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="108">
+      <c r="Q10" s="113">
         <v>0.72</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="107">
         <v>-2.35</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="105">
         <v>4.22</v>
       </c>
-      <c r="T10" s="111">
+      <c r="T10" s="114">
         <v>-33.39</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="123" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4679,40 +4679,40 @@
       <c r="H11">
         <v>10.19</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="121">
         <v>0</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="122">
         <v>10.08</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="127">
         <v>21.01</v>
       </c>
-      <c r="L11" s="124">
+      <c r="L11" s="128">
         <v>25.63</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="125">
         <v>13.45</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="123">
         <v>2.1</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="129">
         <v>-7.56</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="130">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="124">
         <v>-13.03</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="118">
         <v>-11.34</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="119">
         <v>-12.61</v>
       </c>
-      <c r="T11" s="122">
+      <c r="T11" s="120">
         <v>-24.37</v>
       </c>
     </row>
@@ -4741,40 +4741,40 @@
       <c r="H12">
         <v>0.31</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="137">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="143">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="140">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="132">
         <v>-11.67</v>
       </c>
       <c r="M12" s="138">
         <v>-12.05</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="133">
         <v>-11.84</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="134">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="141">
         <v>-14.8</v>
       </c>
       <c r="Q12" s="135">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="131">
         <v>-16.85</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="139">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="140">
+      <c r="T12" s="142">
         <v>-25.11</v>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>300827</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -1.68亿</v>
       </c>
       <c r="E13">
@@ -4803,40 +4803,40 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="153">
         <v>19.01</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="148">
         <v>21.83</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="150">
         <v>18.48</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="154">
         <v>8.85</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="151">
         <v>8.24</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="152">
         <v>7.78</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="155">
         <v>0.85</v>
       </c>
-      <c r="P13" s="153">
+      <c r="P13" s="146">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="147">
         <v>2</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="156">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="149">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="150">
+      <c r="T13" s="144">
         <v>0.37</v>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="169" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,40 +4865,40 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="163">
         <v>3.51</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="160">
         <v>13.88</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="157">
         <v>25.25</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="158">
         <v>32.26</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="166">
         <v>32.76</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="167">
         <v>46.07</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="164">
         <v>51.79</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="159">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="165">
         <v>73.68</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="168">
         <v>56.29</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="161">
         <v>47.35</v>
       </c>
-      <c r="T14" s="165">
+      <c r="T14" s="162">
         <v>44.21</v>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="178" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,40 +4927,40 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="182">
         <v>6.47</v>
       </c>
-      <c r="J15" s="181">
+      <c r="J15" s="177">
         <v>2.54</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="172">
         <v>23.04</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="170">
         <v>12.25</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="173">
         <v>20.11</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="179">
         <v>7.01</v>
       </c>
-      <c r="O15" s="177">
+      <c r="O15" s="174">
         <v>5.08</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="171">
         <v>-0.31</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="175">
         <v>2.23</v>
       </c>
       <c r="R15" s="180">
         <v>1.77</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="176">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="171">
+      <c r="T15" s="181">
         <v>-23.19</v>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4989,40 +4989,40 @@
       <c r="H16">
         <v>-2.65</v>
       </c>
-      <c r="I16" s="184">
+      <c r="I16" s="183">
         <v>1.32</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="184">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="187">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="195">
+      <c r="L16" s="185">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="188">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="193">
         <v>-6.36</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="191">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="194">
         <v>-5.45</v>
       </c>
-      <c r="Q16" s="191">
+      <c r="Q16" s="186">
         <v>-6.32</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="189">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="195">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="183">
+      <c r="T16" s="192">
         <v>-5.68</v>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="205" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,40 +5051,40 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="206">
         <v>0.04</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="200">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="201">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="202">
         <v>-2.98</v>
       </c>
-      <c r="M17" s="196">
+      <c r="M17" s="207">
         <v>-1.75</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="198">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="208">
         <v>-0.79</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="196">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="199">
         <v>-2.22</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="197">
         <v>-2.14</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="203">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="200">
+      <c r="T17" s="204">
         <v>-1.03</v>
       </c>
     </row>
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="214">
+      <c r="I19" s="220">
         <v>87.5</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="210">
         <v>81.25</v>
       </c>
-      <c r="K19" s="218">
+      <c r="K19" s="213">
         <v>75</v>
       </c>
-      <c r="L19" s="209">
+      <c r="L19" s="211">
         <v>75</v>
       </c>
-      <c r="M19" s="210">
+      <c r="M19" s="214">
         <v>75</v>
       </c>
-      <c r="N19" s="211">
+      <c r="N19" s="217">
         <v>68.75</v>
       </c>
-      <c r="O19" s="217">
+      <c r="O19" s="218">
         <v>68.75</v>
       </c>
-      <c r="P19" s="216">
+      <c r="P19" s="212">
         <v>62.5</v>
       </c>
-      <c r="Q19" s="212">
+      <c r="Q19" s="215">
         <v>62.5</v>
       </c>
-      <c r="R19" s="213">
+      <c r="R19" s="216">
         <v>50</v>
       </c>
       <c r="S19" s="219">
         <v>50</v>
       </c>
-      <c r="T19" s="220">
+      <c r="T19" s="209">
         <v>25</v>
       </c>
     </row>
@@ -5195,40 +5195,40 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="231">
+      <c r="I20" s="223">
         <v>7.43</v>
       </c>
-      <c r="J20" s="222">
+      <c r="J20" s="229">
         <v>12.45</v>
       </c>
-      <c r="K20" s="232">
+      <c r="K20" s="224">
         <v>15.15</v>
       </c>
-      <c r="L20" s="230">
+      <c r="L20" s="231">
         <v>14.59</v>
       </c>
-      <c r="M20" s="223">
+      <c r="M20" s="227">
         <v>14.15</v>
       </c>
-      <c r="N20" s="224">
+      <c r="N20" s="232">
         <v>11.63</v>
       </c>
-      <c r="O20" s="225">
+      <c r="O20" s="230">
         <v>11.45</v>
       </c>
-      <c r="P20" s="226">
+      <c r="P20" s="228">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="221">
+      <c r="Q20" s="225">
         <v>10.79</v>
       </c>
-      <c r="R20" s="227">
+      <c r="R20" s="221">
         <v>7.69</v>
       </c>
-      <c r="S20" s="228">
+      <c r="S20" s="222">
         <v>6.9</v>
       </c>
-      <c r="T20" s="229">
+      <c r="T20" s="226">
         <v>-6.8</v>
       </c>
     </row>

--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -45,24 +45,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE9828C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -87,67 +93,667 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB42230"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE15462"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,31 +765,313 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,85 +1083,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,7 +1335,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,1093 +1371,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>002691</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -1601.84万</v>
       </c>
       <c r="E2">
@@ -4121,28 +4121,28 @@
       <c r="H2">
         <v>-2.71</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="13">
         <v>13.05</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="11">
         <v>24.4</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="7">
         <v>36.85</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="4">
         <v>23.21</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="5">
         <v>30.98</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="1">
         <v>28.29</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="8">
         <v>29.48</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="9">
         <v>25.4</v>
       </c>
       <c r="Q2" s="12">
@@ -4151,10 +4151,10 @@
       <c r="R2" s="10">
         <v>8.76</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="2">
         <v>3.09</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="6">
         <v>-27.39</v>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="19" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,37 +4183,37 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="20">
         <v>5.22</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="25">
         <v>15.75</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="14">
         <v>4.21</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="15">
         <v>10.78</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="16">
         <v>8.51</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="21">
         <v>9.52</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="23">
         <v>6.07</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="24">
         <v>2.19</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="17">
         <v>-8</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="22">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="18">
         <v>-12.72</v>
       </c>
       <c r="T3" s="26">
@@ -4245,40 +4245,40 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="32">
         <v>15.18</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="27">
         <v>26.73</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="29">
         <v>39.36</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="36">
         <v>53.27</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="37">
         <v>43.18</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="38">
         <v>29.45</v>
       </c>
       <c r="O4" s="30">
         <v>24.18</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="28">
         <v>23</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="33">
         <v>16.55</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="31">
         <v>16</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="34">
         <v>12</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="35">
         <v>-2.73</v>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="40" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,40 +4307,40 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="49">
         <v>16.27</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="41">
         <v>13.88</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="46">
         <v>14.94</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="52">
         <v>11.32</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="50">
         <v>7.25</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="51">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="42">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="43">
         <v>-8.4</v>
       </c>
       <c r="Q5" s="44">
         <v>-11.23</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="45">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="47">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="48">
         <v>-35.54</v>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>600881</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -413.93万</v>
       </c>
       <c r="E6">
@@ -4369,40 +4369,40 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="58">
         <v>9.64</v>
       </c>
       <c r="J6" s="59">
         <v>13.71</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="55">
         <v>10.66</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="56">
         <v>7.11</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="57">
         <v>5.08</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="65">
         <v>6.09</v>
       </c>
       <c r="O6" s="60">
         <v>7.61</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="53">
         <v>3.55</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="63">
         <v>5.08</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="61">
         <v>4.06</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="62">
         <v>7.61</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="54">
         <v>-20.3</v>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,40 +4431,40 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="67">
         <v>12.74</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="68">
         <v>35.28</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="69">
         <v>44.34</v>
       </c>
       <c r="L7" s="74">
         <v>37.24</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="70">
         <v>52.36</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="71">
         <v>52.32</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="75">
         <v>48.5</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="76">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="77">
         <v>66.56</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="78">
         <v>71.24</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="72">
         <v>61</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="73">
         <v>60.57</v>
       </c>
     </row>
@@ -4496,37 +4496,37 @@
       <c r="I8" s="90">
         <v>10.79</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="83">
         <v>18.2</v>
       </c>
       <c r="K8" s="91">
         <v>12.39</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="84">
         <v>24.77</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="85">
         <v>24.74</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="86">
         <v>21.61</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="79">
         <v>42.12</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="80">
         <v>36.4</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="87">
         <v>40.23</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="81">
         <v>31.84</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="88">
         <v>41.24</v>
       </c>
-      <c r="T8" s="88">
+      <c r="T8" s="82">
         <v>31.5</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4555,40 +4555,40 @@
       <c r="H9">
         <v>2.53</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="98">
         <v>7.31</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="99">
         <v>14.01</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="96">
         <v>11.84</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="92">
         <v>10.5</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="100">
         <v>4.53</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="101">
         <v>1.13</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="93">
         <v>3.09</v>
       </c>
       <c r="P9" s="102">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="94">
         <v>4.33</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="95">
         <v>3.3</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="103">
         <v>5.36</v>
       </c>
-      <c r="T9" s="93">
+      <c r="T9" s="97">
         <v>-8.14</v>
       </c>
     </row>
@@ -4617,40 +4617,40 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="109">
         <v>6.97</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="116">
         <v>3.98</v>
       </c>
-      <c r="K10" s="109">
+      <c r="K10" s="113">
         <v>-2.59</v>
       </c>
       <c r="L10" s="110">
         <v>-2.43</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="107">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="114">
         <v>-0.32</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="111">
         <v>3.94</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="112">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="117">
         <v>0.72</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="115">
         <v>-2.35</v>
       </c>
       <c r="S10" s="105">
         <v>4.22</v>
       </c>
-      <c r="T10" s="114">
+      <c r="T10" s="106">
         <v>-33.39</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="118" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4679,22 +4679,22 @@
       <c r="H11">
         <v>10.19</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="119">
         <v>0</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="120">
         <v>10.08</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="123">
         <v>21.01</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="124">
         <v>25.63</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="127">
         <v>13.45</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="125">
         <v>2.1</v>
       </c>
       <c r="O11" s="129">
@@ -4703,16 +4703,16 @@
       <c r="P11" s="130">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="121">
         <v>-13.03</v>
       </c>
-      <c r="R11" s="118">
+      <c r="R11" s="126">
         <v>-11.34</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="122">
         <v>-12.61</v>
       </c>
-      <c r="T11" s="120">
+      <c r="T11" s="128">
         <v>-24.37</v>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002869</v>
       </c>
-      <c r="D12" s="136" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 798.76万</v>
       </c>
       <c r="E12">
@@ -4741,40 +4741,40 @@
       <c r="H12">
         <v>0.31</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="133">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="136">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="137">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="141">
         <v>-11.67</v>
       </c>
-      <c r="M12" s="138">
+      <c r="M12" s="131">
         <v>-12.05</v>
       </c>
-      <c r="N12" s="133">
+      <c r="N12" s="142">
         <v>-11.84</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="138">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="139">
         <v>-14.8</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="140">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="134">
         <v>-16.85</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="132">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="142">
+      <c r="T12" s="143">
         <v>-25.11</v>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>300827</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="146" t="str">
         <v>净卖: -1.68亿</v>
       </c>
       <c r="E13">
@@ -4803,40 +4803,40 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="144">
         <v>19.01</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="145">
         <v>21.83</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="154">
         <v>18.48</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="151">
         <v>8.85</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="155">
         <v>8.24</v>
       </c>
       <c r="N13" s="152">
         <v>7.78</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="153">
         <v>0.85</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="147">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="148">
         <v>2</v>
       </c>
-      <c r="R13" s="156">
+      <c r="R13" s="149">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="156">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="144">
+      <c r="T13" s="150">
         <v>0.37</v>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="168" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,40 +4865,40 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="161">
         <v>3.51</v>
       </c>
-      <c r="J14" s="160">
+      <c r="J14" s="162">
         <v>13.88</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="163">
         <v>25.25</v>
       </c>
       <c r="L14" s="158">
         <v>32.26</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="169">
         <v>32.76</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="164">
         <v>46.07</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="159">
         <v>51.79</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="166">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="167">
         <v>73.68</v>
       </c>
-      <c r="R14" s="168">
+      <c r="R14" s="157">
         <v>56.29</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="165">
         <v>47.35</v>
       </c>
-      <c r="T14" s="162">
+      <c r="T14" s="160">
         <v>44.21</v>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="178" t="str">
+      <c r="D15" s="175" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,40 +4927,40 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="170">
         <v>6.47</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="172">
         <v>2.54</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="176">
         <v>23.04</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="182">
         <v>12.25</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="177">
         <v>20.11</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="178">
         <v>7.01</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="179">
         <v>5.08</v>
       </c>
       <c r="P15" s="171">
         <v>-0.31</v>
       </c>
-      <c r="Q15" s="175">
+      <c r="Q15" s="173">
         <v>2.23</v>
       </c>
       <c r="R15" s="180">
         <v>1.77</v>
       </c>
-      <c r="S15" s="176">
+      <c r="S15" s="181">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="181">
+      <c r="T15" s="174">
         <v>-23.19</v>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="194" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4989,40 +4989,40 @@
       <c r="H16">
         <v>-2.65</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="195">
         <v>1.32</v>
       </c>
       <c r="J16" s="184">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="185">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="183">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="188">
+      <c r="M16" s="186">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="187">
         <v>-6.36</v>
       </c>
       <c r="O16" s="191">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="194">
+      <c r="P16" s="188">
         <v>-5.45</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="189">
         <v>-6.32</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="192">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="190">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="192">
+      <c r="T16" s="193">
         <v>-5.68</v>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="205" t="str">
+      <c r="D17" s="207" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,40 +5051,40 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="206">
+      <c r="I17" s="198">
         <v>0.04</v>
       </c>
       <c r="J17" s="200">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="208">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="202">
+      <c r="L17" s="196">
         <v>-2.98</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="201">
         <v>-1.75</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="199">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="202">
         <v>-0.79</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="203">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="199">
+      <c r="Q17" s="197">
         <v>-2.22</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="205">
         <v>-2.14</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="204">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="204">
+      <c r="T17" s="206">
         <v>-1.03</v>
       </c>
     </row>
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="220">
+      <c r="I19" s="210">
         <v>87.5</v>
       </c>
-      <c r="J19" s="210">
+      <c r="J19" s="211">
         <v>81.25</v>
       </c>
-      <c r="K19" s="213">
+      <c r="K19" s="218">
         <v>75</v>
       </c>
-      <c r="L19" s="211">
+      <c r="L19" s="212">
         <v>75</v>
       </c>
-      <c r="M19" s="214">
+      <c r="M19" s="213">
         <v>75</v>
       </c>
       <c r="N19" s="217">
         <v>68.75</v>
       </c>
-      <c r="O19" s="218">
+      <c r="O19" s="219">
         <v>68.75</v>
       </c>
-      <c r="P19" s="212">
+      <c r="P19" s="214">
         <v>62.5</v>
       </c>
       <c r="Q19" s="215">
         <v>62.5</v>
       </c>
-      <c r="R19" s="216">
+      <c r="R19" s="220">
         <v>50</v>
       </c>
-      <c r="S19" s="219">
+      <c r="S19" s="209">
         <v>50</v>
       </c>
-      <c r="T19" s="209">
+      <c r="T19" s="216">
         <v>25</v>
       </c>
     </row>
@@ -5195,40 +5195,40 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="223">
+      <c r="I20" s="231">
         <v>7.43</v>
       </c>
-      <c r="J20" s="229">
+      <c r="J20" s="227">
         <v>12.45</v>
       </c>
-      <c r="K20" s="224">
+      <c r="K20" s="228">
         <v>15.15</v>
       </c>
-      <c r="L20" s="231">
+      <c r="L20" s="224">
         <v>14.59</v>
       </c>
-      <c r="M20" s="227">
+      <c r="M20" s="225">
         <v>14.15</v>
       </c>
-      <c r="N20" s="232">
+      <c r="N20" s="229">
         <v>11.63</v>
       </c>
       <c r="O20" s="230">
         <v>11.45</v>
       </c>
-      <c r="P20" s="228">
+      <c r="P20" s="232">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="225">
+      <c r="Q20" s="221">
         <v>10.79</v>
       </c>
-      <c r="R20" s="221">
+      <c r="R20" s="223">
         <v>7.69</v>
       </c>
-      <c r="S20" s="222">
+      <c r="S20" s="226">
         <v>6.9</v>
       </c>
-      <c r="T20" s="226">
+      <c r="T20" s="222">
         <v>-6.8</v>
       </c>
     </row>

--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -39,6 +39,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -51,6 +87,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -63,7 +135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1F8337"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,37 +147,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,19 +165,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB62432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,19 +189,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,19 +279,457 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,67 +747,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -273,6 +759,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -285,7 +969,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,451 +1149,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -759,558 +1329,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -1329,25 +1347,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>002691</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -1601.84万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>-2.71</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="5">
         <v>13.05</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9">
         <v>24.4</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="10">
         <v>36.85</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>23.21</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="7">
         <v>30.98</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="12">
         <v>28.29</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="2">
         <v>29.48</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="3">
         <v>25.4</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="13">
         <v>20.82</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="1">
         <v>8.76</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="8">
         <v>3.09</v>
       </c>
       <c r="T2" s="6">
-        <v>-27.39</v>
+        <v>-26.99</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,25 +4183,25 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="19">
         <v>5.22</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="20">
         <v>15.75</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="21">
         <v>4.21</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="16">
         <v>10.78</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="22">
         <v>8.51</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="23">
         <v>9.52</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="14">
         <v>6.07</v>
       </c>
       <c r="P3" s="24">
@@ -4210,14 +4210,14 @@
       <c r="Q3" s="17">
         <v>-8</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="25">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="26">
         <v>-12.72</v>
       </c>
-      <c r="T3" s="26">
-        <v>-38.58</v>
+      <c r="T3" s="18">
+        <v>-38.25</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>000856</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -799.12万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="34">
         <v>15.18</v>
       </c>
       <c r="J4" s="27">
         <v>26.73</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="35">
         <v>39.36</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>53.27</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="28">
         <v>43.18</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="36">
         <v>29.45</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="37">
         <v>24.18</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="29">
         <v>23</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="30">
         <v>16.55</v>
       </c>
       <c r="R4" s="31">
         <v>16</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="32">
         <v>12</v>
       </c>
-      <c r="T4" s="35">
-        <v>-2.73</v>
+      <c r="T4" s="33">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="42">
         <v>16.27</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="48">
         <v>13.88</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="43">
         <v>14.94</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="51">
         <v>11.32</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="44">
         <v>7.25</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="45">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="46">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="49">
         <v>-8.4</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="50">
         <v>-11.23</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="52">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="40">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="48">
-        <v>-35.54</v>
+      <c r="T5" s="47">
+        <v>-35.19</v>
       </c>
     </row>
     <row r="6">
@@ -4369,40 +4369,40 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="54">
         <v>9.64</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="61">
         <v>13.71</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="62">
         <v>10.66</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="65">
         <v>7.11</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="55">
         <v>5.08</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="56">
         <v>6.09</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="58">
         <v>7.61</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="59">
         <v>3.55</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="57">
         <v>5.08</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="60">
         <v>4.06</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="63">
         <v>7.61</v>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="53">
         <v>-20.3</v>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,7 +4431,7 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="75">
         <v>12.74</v>
       </c>
       <c r="J7" s="68">
@@ -4440,32 +4440,32 @@
       <c r="K7" s="69">
         <v>44.34</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="76">
         <v>37.24</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="71">
         <v>52.36</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="77">
         <v>52.32</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="72">
         <v>48.5</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="66">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="73">
         <v>66.56</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="70">
         <v>71.24</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="74">
         <v>61</v>
       </c>
-      <c r="T7" s="73">
-        <v>60.57</v>
+      <c r="T7" s="78">
+        <v>59.93</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>301488</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -1455.69万</v>
       </c>
       <c r="E8">
@@ -4493,41 +4493,41 @@
       <c r="H8">
         <v>8.31</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="85">
         <v>10.79</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="86">
         <v>18.2</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="79">
         <v>12.39</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="87">
         <v>24.77</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="81">
         <v>24.74</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="80">
         <v>21.61</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="82">
         <v>42.12</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="83">
         <v>36.4</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="84">
         <v>40.23</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="88">
         <v>31.84</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="89">
         <v>41.24</v>
       </c>
-      <c r="T8" s="82">
-        <v>31.5</v>
+      <c r="T8" s="90">
+        <v>30.97</v>
       </c>
     </row>
     <row r="9">
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.53</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="96">
         <v>7.31</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="97">
         <v>14.01</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="98">
         <v>11.84</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="103">
         <v>10.5</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="102">
         <v>4.53</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="99">
         <v>1.13</v>
       </c>
-      <c r="O9" s="93">
+      <c r="O9" s="92">
         <v>3.09</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="100">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="104">
         <v>4.33</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="101">
         <v>3.3</v>
       </c>
-      <c r="S9" s="103">
+      <c r="S9" s="93">
         <v>5.36</v>
       </c>
-      <c r="T9" s="97">
-        <v>-8.14</v>
+      <c r="T9" s="94">
+        <v>-7.31</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>603595</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 1022.73万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="105">
         <v>6.97</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="109">
         <v>3.98</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="106">
         <v>-2.59</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="111">
         <v>-2.43</v>
       </c>
       <c r="M10" s="107">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="115">
         <v>-0.32</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="112">
         <v>3.94</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="113">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="114">
         <v>0.72</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="108">
         <v>-2.35</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="116">
         <v>4.22</v>
       </c>
-      <c r="T10" s="106">
-        <v>-33.39</v>
+      <c r="T10" s="117">
+        <v>-30.04</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="120" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4679,22 +4679,22 @@
       <c r="H11">
         <v>10.19</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="124">
         <v>0</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="118">
         <v>10.08</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="121">
         <v>21.01</v>
       </c>
-      <c r="L11" s="124">
+      <c r="L11" s="126">
         <v>25.63</v>
       </c>
       <c r="M11" s="127">
         <v>13.45</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="128">
         <v>2.1</v>
       </c>
       <c r="O11" s="129">
@@ -4703,17 +4703,17 @@
       <c r="P11" s="130">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="122">
         <v>-13.03</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="123">
         <v>-11.34</v>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="125">
         <v>-12.61</v>
       </c>
-      <c r="T11" s="128">
-        <v>-24.37</v>
+      <c r="T11" s="119">
+        <v>-24.79</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002869</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="133" t="str">
         <v>净买: 798.76万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>0.31</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="134">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="143">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="135">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="138">
         <v>-11.67</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="139">
         <v>-12.05</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="131">
         <v>-11.84</v>
       </c>
-      <c r="O12" s="138">
+      <c r="O12" s="136">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="140">
         <v>-14.8</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="141">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="142">
         <v>-16.85</v>
       </c>
       <c r="S12" s="132">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="143">
-        <v>-25.11</v>
+      <c r="T12" s="137">
+        <v>-24.73</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>300827</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="154" t="str">
         <v>净卖: -1.68亿</v>
       </c>
       <c r="E13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="149">
         <v>19.01</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="155">
         <v>21.83</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="152">
         <v>18.48</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="150">
         <v>8.85</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="156">
         <v>8.24</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="144">
         <v>7.78</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="145">
         <v>0.85</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="146">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="151">
         <v>2</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="153">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="147">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="150">
-        <v>0.37</v>
+      <c r="T13" s="148">
+        <v>1.57</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="167">
         <v>3.51</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="165">
         <v>13.88</v>
       </c>
-      <c r="K14" s="163">
+      <c r="K14" s="158">
         <v>25.25</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="168">
         <v>32.26</v>
       </c>
       <c r="M14" s="169">
         <v>32.76</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="166">
         <v>46.07</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="157">
         <v>51.79</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="159">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="163">
         <v>73.68</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="160">
         <v>56.29</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="161">
         <v>47.35</v>
       </c>
-      <c r="T14" s="160">
-        <v>44.21</v>
+      <c r="T14" s="162">
+        <v>46.14</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="179" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="173">
         <v>6.47</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="174">
         <v>2.54</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="182">
         <v>23.04</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="170">
         <v>12.25</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="171">
         <v>20.11</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="175">
         <v>7.01</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="180">
         <v>5.08</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="181">
         <v>-0.31</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="172">
         <v>2.23</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="176">
         <v>1.77</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="177">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="174">
-        <v>-23.19</v>
+      <c r="T15" s="178">
+        <v>-22.19</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="195" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-2.65</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="189">
         <v>1.32</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="190">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="186">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="191">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="192">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="183">
         <v>-6.36</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="187">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="193">
         <v>-5.45</v>
       </c>
-      <c r="Q16" s="189">
+      <c r="Q16" s="184">
         <v>-6.32</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="188">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="194">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="193">
-        <v>-5.68</v>
+      <c r="T16" s="185">
+        <v>-8.4</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="208" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="203">
         <v>0.04</v>
       </c>
-      <c r="J17" s="200">
+      <c r="J17" s="204">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="196">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="197">
         <v>-2.98</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="198">
         <v>-1.75</v>
       </c>
       <c r="N17" s="199">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="200">
         <v>-0.79</v>
       </c>
-      <c r="P17" s="203">
+      <c r="P17" s="201">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="206">
         <v>-2.22</v>
       </c>
       <c r="R17" s="205">
         <v>-2.14</v>
       </c>
-      <c r="S17" s="204">
+      <c r="S17" s="202">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="206">
-        <v>-1.03</v>
+      <c r="T17" s="207">
+        <v>-3.89</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="210">
+      <c r="I19" s="215">
         <v>87.5</v>
       </c>
-      <c r="J19" s="211">
+      <c r="J19" s="210">
         <v>81.25</v>
       </c>
-      <c r="K19" s="218">
+      <c r="K19" s="211">
         <v>75</v>
       </c>
-      <c r="L19" s="212">
+      <c r="L19" s="219">
         <v>75</v>
       </c>
-      <c r="M19" s="213">
+      <c r="M19" s="216">
         <v>75</v>
       </c>
-      <c r="N19" s="217">
+      <c r="N19" s="212">
         <v>68.75</v>
       </c>
-      <c r="O19" s="219">
+      <c r="O19" s="213">
         <v>68.75</v>
       </c>
-      <c r="P19" s="214">
+      <c r="P19" s="217">
         <v>62.5</v>
       </c>
-      <c r="Q19" s="215">
+      <c r="Q19" s="218">
         <v>62.5</v>
       </c>
       <c r="R19" s="220">
         <v>50</v>
       </c>
-      <c r="S19" s="209">
+      <c r="S19" s="214">
         <v>50</v>
       </c>
-      <c r="T19" s="216">
+      <c r="T19" s="209">
         <v>25</v>
       </c>
     </row>
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="231">
+      <c r="I20" s="225">
         <v>7.43</v>
       </c>
-      <c r="J20" s="227">
+      <c r="J20" s="226">
         <v>12.45</v>
       </c>
-      <c r="K20" s="228">
+      <c r="K20" s="227">
         <v>15.15</v>
       </c>
-      <c r="L20" s="224">
+      <c r="L20" s="228">
         <v>14.59</v>
       </c>
-      <c r="M20" s="225">
+      <c r="M20" s="229">
         <v>14.15</v>
       </c>
-      <c r="N20" s="229">
+      <c r="N20" s="230">
         <v>11.63</v>
       </c>
-      <c r="O20" s="230">
+      <c r="O20" s="231">
         <v>11.45</v>
       </c>
-      <c r="P20" s="232">
+      <c r="P20" s="223">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="221">
+      <c r="Q20" s="232">
         <v>10.79</v>
       </c>
-      <c r="R20" s="223">
+      <c r="R20" s="221">
         <v>7.69</v>
       </c>
-      <c r="S20" s="226">
+      <c r="S20" s="224">
         <v>6.9</v>
       </c>
       <c r="T20" s="222">
-        <v>-6.8</v>
+        <v>-6.52</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -39,24 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB42230"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -75,7 +123,535 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,37 +663,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,54 +819,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -195,67 +837,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,6 +921,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -279,6 +1059,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -297,19 +1101,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,13 +1203,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,1087 +1365,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>002691</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -1601.84万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>-2.71</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="13">
         <v>13.05</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="4">
         <v>24.4</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="1">
         <v>36.85</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="8">
         <v>23.21</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="9">
         <v>30.98</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="5">
         <v>28.29</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="10">
         <v>29.48</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="6">
         <v>25.4</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="2">
         <v>20.82</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="11">
         <v>8.76</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="3">
         <v>3.09</v>
       </c>
-      <c r="T2" s="6">
-        <v>-26.99</v>
+      <c r="T2" s="7">
+        <v>-29.28</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="20" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="16">
         <v>5.22</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="26">
         <v>15.75</v>
       </c>
       <c r="K3" s="21">
         <v>4.21</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="17">
         <v>10.78</v>
       </c>
       <c r="M3" s="22">
         <v>8.51</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="18">
         <v>9.52</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="23">
         <v>6.07</v>
       </c>
       <c r="P3" s="24">
         <v>2.19</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="25">
         <v>-8</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="14">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="19">
         <v>-12.72</v>
       </c>
-      <c r="T3" s="18">
-        <v>-38.25</v>
+      <c r="T3" s="15">
+        <v>-40.19</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>000856</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -799.12万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="28">
         <v>15.18</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="30">
         <v>26.73</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="33">
         <v>39.36</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="36">
         <v>53.27</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="31">
         <v>43.18</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="37">
         <v>29.45</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="32">
         <v>24.18</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="34">
         <v>23</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="38">
         <v>16.55</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="35">
         <v>16</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="39">
         <v>12</v>
       </c>
-      <c r="T4" s="33">
-        <v>-0.91</v>
+      <c r="T4" s="27">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="50">
         <v>16.27</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="44">
         <v>13.88</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="41">
         <v>14.94</v>
       </c>
       <c r="L5" s="51">
         <v>11.32</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="45">
         <v>7.25</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="52">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="47">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="42">
         <v>-8.4</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="46">
         <v>-11.23</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="40">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="48">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="47">
-        <v>-35.19</v>
+      <c r="T5" s="49">
+        <v>-37.22</v>
       </c>
     </row>
     <row r="6">
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>600881</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -413.93万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="60">
         <v>9.64</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="58">
         <v>13.71</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="57">
         <v>10.66</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="61">
         <v>7.11</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="65">
         <v>5.08</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="59">
         <v>6.09</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="53">
         <v>7.61</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="62">
         <v>3.55</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="63">
         <v>5.08</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="64">
         <v>4.06</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="54">
         <v>7.61</v>
       </c>
-      <c r="T6" s="53">
-        <v>-20.3</v>
+      <c r="T6" s="55">
+        <v>-20.81</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="72" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="78">
         <v>12.74</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="73">
         <v>35.28</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="74">
         <v>44.34</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="68">
         <v>37.24</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="75">
         <v>52.36</v>
       </c>
-      <c r="N7" s="77">
+      <c r="N7" s="69">
         <v>52.32</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="76">
         <v>48.5</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="77">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="73">
+      <c r="Q7" s="70">
         <v>66.56</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="71">
         <v>71.24</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="66">
         <v>61</v>
       </c>
-      <c r="T7" s="78">
-        <v>59.93</v>
+      <c r="T7" s="67">
+        <v>59.24</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>301488</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="81" t="str">
         <v>净卖: -1455.69万</v>
       </c>
       <c r="E8">
@@ -4493,41 +4493,41 @@
       <c r="H8">
         <v>8.31</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="79">
         <v>10.79</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="89">
         <v>18.2</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="82">
         <v>12.39</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="80">
         <v>24.77</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="83">
         <v>24.74</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="90">
         <v>21.61</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="84">
         <v>42.12</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="85">
         <v>36.4</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="91">
         <v>40.23</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="87">
         <v>31.84</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="86">
         <v>41.24</v>
       </c>
-      <c r="T8" s="90">
-        <v>30.97</v>
+      <c r="T8" s="88">
+        <v>30.4</v>
       </c>
     </row>
     <row r="9">
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4555,7 +4555,7 @@
       <c r="H9">
         <v>2.53</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="101">
         <v>7.31</v>
       </c>
       <c r="J9" s="97">
@@ -4564,32 +4564,32 @@
       <c r="K9" s="98">
         <v>11.84</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="99">
         <v>10.5</v>
       </c>
       <c r="M9" s="102">
         <v>4.53</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="95">
         <v>1.13</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="104">
         <v>3.09</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="92">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="93">
         <v>4.33</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="103">
         <v>3.3</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="100">
         <v>5.36</v>
       </c>
       <c r="T9" s="94">
-        <v>-7.31</v>
+        <v>-8.55</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>603595</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="106" t="str">
         <v>净买: 1022.73万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="107">
         <v>6.97</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="105">
         <v>3.98</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="114">
         <v>-2.59</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="115">
         <v>-2.43</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="111">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="108">
         <v>-0.32</v>
       </c>
       <c r="O10" s="112">
         <v>3.94</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="109">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="113">
         <v>0.72</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="116">
         <v>-2.35</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="110">
         <v>4.22</v>
       </c>
       <c r="T10" s="117">
-        <v>-30.04</v>
+        <v>-27.81</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="129" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4682,37 +4682,37 @@
       <c r="I11" s="124">
         <v>0</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="125">
         <v>10.08</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="130">
         <v>21.01</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="118">
         <v>25.63</v>
       </c>
-      <c r="M11" s="127">
+      <c r="M11" s="122">
         <v>13.45</v>
       </c>
-      <c r="N11" s="128">
+      <c r="N11" s="126">
         <v>2.1</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="121">
         <v>-7.56</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="119">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="127">
         <v>-13.03</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="120">
         <v>-11.34</v>
       </c>
-      <c r="S11" s="125">
+      <c r="S11" s="128">
         <v>-12.61</v>
       </c>
-      <c r="T11" s="119">
+      <c r="T11" s="123">
         <v>-24.79</v>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002869</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="137" t="str">
         <v>净买: 798.76万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>0.31</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="138">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="141">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="142">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="134">
         <v>-11.67</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="135">
         <v>-12.05</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="136">
         <v>-11.84</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="132">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="140">
+      <c r="P12" s="143">
         <v>-14.8</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="139">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="142">
+      <c r="R12" s="131">
         <v>-16.85</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="140">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="137">
-        <v>-24.73</v>
+      <c r="T12" s="133">
+        <v>-25.67</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>300827</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="147" t="str">
         <v>净卖: -1.68亿</v>
       </c>
       <c r="E13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="152">
         <v>19.01</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="153">
         <v>21.83</v>
       </c>
-      <c r="K13" s="152">
+      <c r="K13" s="144">
         <v>18.48</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="145">
         <v>8.85</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="148">
         <v>8.24</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="146">
         <v>7.78</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="149">
         <v>0.85</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="154">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="155">
         <v>2</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="150">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="147">
+      <c r="S13" s="151">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="148">
-        <v>1.57</v>
+      <c r="T13" s="156">
+        <v>0.27</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="164" t="str">
+      <c r="D14" s="162" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="158">
         <v>3.51</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="163">
         <v>13.88</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="169">
         <v>25.25</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="159">
         <v>32.26</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="160">
         <v>32.76</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="164">
         <v>46.07</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="167">
         <v>51.79</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="157">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="165">
         <v>73.68</v>
       </c>
-      <c r="R14" s="160">
+      <c r="R14" s="166">
         <v>56.29</v>
       </c>
       <c r="S14" s="161">
         <v>47.35</v>
       </c>
-      <c r="T14" s="162">
-        <v>46.14</v>
+      <c r="T14" s="168">
+        <v>47.85</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="175" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="171">
         <v>6.47</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="172">
         <v>2.54</v>
       </c>
-      <c r="K15" s="182">
+      <c r="K15" s="176">
         <v>23.04</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="177">
         <v>12.25</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="178">
         <v>20.11</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="173">
         <v>7.01</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="174">
         <v>5.08</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="180">
         <v>-0.31</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="181">
         <v>2.23</v>
       </c>
-      <c r="R15" s="176">
+      <c r="R15" s="179">
         <v>1.77</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="182">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="178">
-        <v>-22.19</v>
+      <c r="T15" s="170">
+        <v>-23.34</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="189" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-2.65</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="193">
         <v>1.32</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="195">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="183">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="190">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="191">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="187">
         <v>-6.36</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="184">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="185">
         <v>-5.45</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="186">
         <v>-6.32</v>
       </c>
       <c r="R16" s="188">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="192">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="185">
-        <v>-8.4</v>
+      <c r="T16" s="194">
+        <v>-10.1</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="208" t="str">
+      <c r="D17" s="203" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="200">
         <v>0.04</v>
       </c>
       <c r="J17" s="204">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="205">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="198">
         <v>-2.98</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="206">
         <v>-1.75</v>
       </c>
       <c r="N17" s="199">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="207">
         <v>-0.79</v>
       </c>
       <c r="P17" s="201">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="208">
         <v>-2.22</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="196">
         <v>-2.14</v>
       </c>
       <c r="S17" s="202">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="207">
-        <v>-3.89</v>
+      <c r="T17" s="197">
+        <v>-5.68</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="215">
+      <c r="I19" s="214">
         <v>87.5</v>
       </c>
-      <c r="J19" s="210">
+      <c r="J19" s="215">
         <v>81.25</v>
       </c>
-      <c r="K19" s="211">
+      <c r="K19" s="209">
         <v>75</v>
       </c>
-      <c r="L19" s="219">
+      <c r="L19" s="216">
         <v>75</v>
       </c>
-      <c r="M19" s="216">
+      <c r="M19" s="218">
         <v>75</v>
       </c>
-      <c r="N19" s="212">
+      <c r="N19" s="213">
         <v>68.75</v>
       </c>
-      <c r="O19" s="213">
+      <c r="O19" s="210">
         <v>68.75</v>
       </c>
       <c r="P19" s="217">
         <v>62.5</v>
       </c>
-      <c r="Q19" s="218">
+      <c r="Q19" s="211">
         <v>62.5</v>
       </c>
-      <c r="R19" s="220">
+      <c r="R19" s="219">
         <v>50</v>
       </c>
-      <c r="S19" s="214">
+      <c r="S19" s="212">
         <v>50</v>
       </c>
-      <c r="T19" s="209">
+      <c r="T19" s="220">
         <v>25</v>
       </c>
     </row>
@@ -5195,10 +5195,10 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="225">
+      <c r="I20" s="226">
         <v>7.43</v>
       </c>
-      <c r="J20" s="226">
+      <c r="J20" s="221">
         <v>12.45</v>
       </c>
       <c r="K20" s="227">
@@ -5207,29 +5207,29 @@
       <c r="L20" s="228">
         <v>14.59</v>
       </c>
-      <c r="M20" s="229">
+      <c r="M20" s="222">
         <v>14.15</v>
       </c>
-      <c r="N20" s="230">
+      <c r="N20" s="229">
         <v>11.63</v>
       </c>
-      <c r="O20" s="231">
+      <c r="O20" s="230">
         <v>11.45</v>
       </c>
       <c r="P20" s="223">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="232">
+      <c r="Q20" s="224">
         <v>10.79</v>
       </c>
-      <c r="R20" s="221">
+      <c r="R20" s="225">
         <v>7.69</v>
       </c>
-      <c r="S20" s="224">
+      <c r="S20" s="231">
         <v>6.9</v>
       </c>
-      <c r="T20" s="222">
-        <v>-6.52</v>
+      <c r="T20" s="232">
+        <v>-7.41</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -51,6 +51,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE9828C"/>
         <bgColor/>
       </patternFill>
@@ -63,13 +117,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,25 +147,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,7 +177,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,25 +303,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,55 +333,445 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE15462"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,61 +783,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,13 +819,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,13 +921,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,7 +1083,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,451 +1293,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -789,505 +1335,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1299,61 +1353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>002691</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -1601.84万</v>
       </c>
       <c r="E2">
@@ -4124,38 +4124,38 @@
       <c r="I2" s="13">
         <v>13.05</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>24.4</v>
       </c>
       <c r="K2" s="1">
         <v>36.85</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="2">
         <v>23.21</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="10">
         <v>30.98</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="6">
         <v>28.29</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="11">
         <v>29.48</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="7">
         <v>25.4</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="8">
         <v>20.82</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="3">
         <v>8.76</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="12">
         <v>3.09</v>
       </c>
-      <c r="T2" s="7">
-        <v>-29.28</v>
+      <c r="T2" s="9">
+        <v>-38.75</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <v>5.22</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="20">
         <v>15.75</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="24">
         <v>4.21</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="16">
         <v>10.78</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="17">
         <v>8.51</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="25">
         <v>9.52</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="21">
         <v>6.07</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="26">
         <v>2.19</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="14">
         <v>-8</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="18">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="22">
         <v>-12.72</v>
       </c>
-      <c r="T3" s="15">
-        <v>-40.19</v>
+      <c r="T3" s="19">
+        <v>-48.19</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>000856</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -799.12万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="38">
         <v>15.18</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="28">
         <v>26.73</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="35">
         <v>39.36</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="33">
         <v>53.27</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="29">
         <v>43.18</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="30">
         <v>29.45</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="34">
         <v>24.18</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="36">
         <v>23</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="31">
         <v>16.55</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="32">
         <v>16</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="37">
         <v>12</v>
       </c>
-      <c r="T4" s="27">
-        <v>-2.91</v>
+      <c r="T4" s="39">
+        <v>-4.91</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="40" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,16 +4307,16 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="47">
         <v>16.27</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="51">
         <v>13.88</v>
       </c>
       <c r="K5" s="41">
         <v>14.94</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="48">
         <v>11.32</v>
       </c>
       <c r="M5" s="45">
@@ -4325,23 +4325,23 @@
       <c r="N5" s="52">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="42">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="43">
         <v>-8.4</v>
       </c>
       <c r="Q5" s="46">
         <v>-11.23</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="49">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="44">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="49">
-        <v>-37.22</v>
+      <c r="T5" s="50">
+        <v>-45.62</v>
       </c>
     </row>
     <row r="6">
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>600881</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -413.93万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="55">
         <v>9.64</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="53">
         <v>13.71</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="59">
         <v>10.66</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="60">
         <v>7.11</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="56">
         <v>5.08</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="57">
         <v>6.09</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="58">
         <v>7.61</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="64">
         <v>3.55</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="65">
         <v>5.08</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="54">
         <v>4.06</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="61">
         <v>7.61</v>
       </c>
-      <c r="T6" s="55">
-        <v>-20.81</v>
+      <c r="T6" s="62">
+        <v>-26.9</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="72" t="str">
+      <c r="D7" s="69" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="70">
         <v>12.74</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="77">
         <v>35.28</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="71">
         <v>44.34</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="72">
         <v>37.24</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="67">
         <v>52.36</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="73">
         <v>52.32</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="78">
         <v>48.5</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="66">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="75">
         <v>66.56</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="68">
         <v>71.24</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="74">
         <v>61</v>
       </c>
-      <c r="T7" s="67">
-        <v>59.24</v>
+      <c r="T7" s="76">
+        <v>51.7</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>301488</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="80" t="str">
         <v>净卖: -1455.69万</v>
       </c>
       <c r="E8">
@@ -4493,41 +4493,41 @@
       <c r="H8">
         <v>8.31</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="90">
         <v>10.79</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="81">
         <v>18.2</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="87">
         <v>12.39</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="91">
         <v>24.77</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="84">
         <v>24.74</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="82">
         <v>21.61</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="83">
         <v>42.12</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="79">
         <v>36.4</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="88">
         <v>40.23</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="89">
         <v>31.84</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="85">
         <v>41.24</v>
       </c>
-      <c r="T8" s="88">
-        <v>30.4</v>
+      <c r="T8" s="86">
+        <v>24.23</v>
       </c>
     </row>
     <row r="9">
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="93" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4558,38 +4558,38 @@
       <c r="I9" s="101">
         <v>7.31</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="104">
         <v>14.01</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="94">
         <v>11.84</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="102">
         <v>10.5</v>
       </c>
-      <c r="M9" s="102">
+      <c r="M9" s="95">
         <v>4.53</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="99">
         <v>1.13</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="92">
         <v>3.09</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="96">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="97">
         <v>4.33</v>
       </c>
       <c r="R9" s="103">
         <v>3.3</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="98">
         <v>5.36</v>
       </c>
-      <c r="T9" s="94">
-        <v>-8.55</v>
+      <c r="T9" s="100">
+        <v>-10.4</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>603595</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="113" t="str">
         <v>净买: 1022.73万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="114">
         <v>6.97</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="115">
         <v>3.98</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="105">
         <v>-2.59</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="116">
         <v>-2.43</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="106">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="107">
         <v>-0.32</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="108">
         <v>3.94</v>
       </c>
       <c r="P10" s="109">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="110">
         <v>0.72</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="117">
         <v>-2.35</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="112">
         <v>4.22</v>
       </c>
-      <c r="T10" s="117">
-        <v>-27.81</v>
+      <c r="T10" s="111">
+        <v>-25.98</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4679,41 +4679,41 @@
       <c r="H11">
         <v>10.19</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="128">
         <v>0</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="119">
         <v>10.08</v>
       </c>
-      <c r="K11" s="130">
+      <c r="K11" s="120">
         <v>21.01</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="126">
         <v>25.63</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="121">
         <v>13.45</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="129">
         <v>2.1</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="127">
         <v>-7.56</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="125">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="122">
         <v>-13.03</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="130">
         <v>-11.34</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="123">
         <v>-12.61</v>
       </c>
-      <c r="T11" s="123">
-        <v>-24.79</v>
+      <c r="T11" s="118">
+        <v>-26.89</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002869</v>
       </c>
-      <c r="D12" s="137" t="str">
+      <c r="D12" s="134" t="str">
         <v>净买: 798.76万</v>
       </c>
       <c r="E12">
@@ -4741,19 +4741,19 @@
       <c r="H12">
         <v>0.31</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="139">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="135">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="143">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="140">
         <v>-11.67</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="131">
         <v>-12.05</v>
       </c>
       <c r="N12" s="136">
@@ -4762,20 +4762,20 @@
       <c r="O12" s="132">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="143">
+      <c r="P12" s="137">
         <v>-14.8</v>
       </c>
-      <c r="Q12" s="139">
+      <c r="Q12" s="142">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="138">
         <v>-16.85</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="133">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="133">
-        <v>-25.67</v>
+      <c r="T12" s="141">
+        <v>-26.29</v>
       </c>
     </row>
     <row r="13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="151">
         <v>19.01</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="154">
         <v>21.83</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="156">
         <v>18.48</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="155">
         <v>8.85</v>
       </c>
       <c r="M13" s="148">
         <v>8.24</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="149">
         <v>7.78</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="144">
         <v>0.85</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="145">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="152">
         <v>2</v>
       </c>
       <c r="R13" s="150">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="153">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="156">
-        <v>0.27</v>
+      <c r="T13" s="146">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="168">
         <v>3.51</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="164">
         <v>13.88</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="165">
         <v>25.25</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="169">
         <v>32.26</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="166">
         <v>32.76</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="159">
         <v>46.07</v>
       </c>
       <c r="O14" s="167">
         <v>51.79</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="160">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="157">
         <v>73.68</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="161">
         <v>56.29</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="162">
         <v>47.35</v>
       </c>
-      <c r="T14" s="168">
-        <v>47.85</v>
+      <c r="T14" s="163">
+        <v>47.5</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="177" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,25 +4927,25 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="175">
         <v>6.47</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="176">
         <v>2.54</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="179">
         <v>23.04</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="170">
         <v>12.25</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="171">
         <v>20.11</v>
       </c>
-      <c r="N15" s="173">
+      <c r="N15" s="172">
         <v>7.01</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="178">
         <v>5.08</v>
       </c>
       <c r="P15" s="180">
@@ -4954,14 +4954,14 @@
       <c r="Q15" s="181">
         <v>2.23</v>
       </c>
-      <c r="R15" s="179">
+      <c r="R15" s="173">
         <v>1.77</v>
       </c>
       <c r="S15" s="182">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="170">
-        <v>-23.34</v>
+      <c r="T15" s="174">
+        <v>-26.96</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4992,38 +4992,38 @@
       <c r="I16" s="193">
         <v>1.32</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="187">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="188">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="190">
+      <c r="L16" s="194">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="189">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="195">
         <v>-6.36</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="185">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="183">
         <v>-5.45</v>
       </c>
       <c r="Q16" s="186">
         <v>-6.32</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="190">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="191">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="194">
-        <v>-10.1</v>
+      <c r="T16" s="184">
+        <v>-9.88</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="200" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="204">
         <v>0.04</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="203">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="201">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="205">
         <v>-2.98</v>
       </c>
       <c r="M17" s="206">
         <v>-1.75</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="207">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="208">
         <v>-0.79</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="202">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="197">
         <v>-2.22</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="198">
         <v>-2.14</v>
       </c>
-      <c r="S17" s="202">
+      <c r="S17" s="196">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="197">
-        <v>-5.68</v>
+      <c r="T17" s="199">
+        <v>-5.44</v>
       </c>
     </row>
     <row r="18">
@@ -5147,41 +5147,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="214">
+      <c r="I19" s="216">
         <v>87.5</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="217">
         <v>81.25</v>
       </c>
-      <c r="K19" s="209">
+      <c r="K19" s="210">
         <v>75</v>
       </c>
-      <c r="L19" s="216">
+      <c r="L19" s="211">
         <v>75</v>
       </c>
-      <c r="M19" s="218">
+      <c r="M19" s="212">
         <v>75</v>
       </c>
       <c r="N19" s="213">
         <v>68.75</v>
       </c>
-      <c r="O19" s="210">
+      <c r="O19" s="219">
         <v>68.75</v>
       </c>
-      <c r="P19" s="217">
+      <c r="P19" s="218">
         <v>62.5</v>
       </c>
-      <c r="Q19" s="211">
+      <c r="Q19" s="214">
         <v>62.5</v>
       </c>
-      <c r="R19" s="219">
+      <c r="R19" s="220">
         <v>50</v>
       </c>
-      <c r="S19" s="212">
+      <c r="S19" s="215">
         <v>50</v>
       </c>
-      <c r="T19" s="220">
-        <v>25</v>
+      <c r="T19" s="209">
+        <v>18.75</v>
       </c>
     </row>
     <row r="20">
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="226">
+      <c r="I20" s="228">
         <v>7.43</v>
       </c>
-      <c r="J20" s="221">
+      <c r="J20" s="223">
         <v>12.45</v>
       </c>
-      <c r="K20" s="227">
+      <c r="K20" s="221">
         <v>15.15</v>
       </c>
-      <c r="L20" s="228">
+      <c r="L20" s="224">
         <v>14.59</v>
       </c>
-      <c r="M20" s="222">
+      <c r="M20" s="229">
         <v>14.15</v>
       </c>
-      <c r="N20" s="229">
+      <c r="N20" s="225">
         <v>11.63</v>
       </c>
       <c r="O20" s="230">
         <v>11.45</v>
       </c>
-      <c r="P20" s="223">
+      <c r="P20" s="231">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="224">
+      <c r="Q20" s="222">
         <v>10.79</v>
       </c>
-      <c r="R20" s="225">
+      <c r="R20" s="226">
         <v>7.69</v>
       </c>
-      <c r="S20" s="231">
+      <c r="S20" s="227">
         <v>6.9</v>
       </c>
       <c r="T20" s="232">
-        <v>-7.41</v>
+        <v>-10.88</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -39,6 +39,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -57,6 +87,102 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -75,13 +201,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,13 +315,283 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,31 +603,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,19 +651,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,25 +747,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,67 +963,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA848"/>
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,19 +1047,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,7 +1131,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,1105 +1353,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>002691</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -1601.84万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>-2.71</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="4">
         <v>13.05</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="9">
         <v>24.4</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="10">
         <v>36.85</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="12">
         <v>23.21</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="5">
         <v>30.98</v>
       </c>
       <c r="N2" s="6">
         <v>28.29</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="7">
         <v>29.48</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="13">
         <v>25.4</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="2">
         <v>20.82</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="8">
         <v>8.76</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="1">
         <v>3.09</v>
       </c>
-      <c r="T2" s="9">
-        <v>-38.75</v>
+      <c r="T2" s="11">
+        <v>-44.82</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="22">
         <v>5.22</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="26">
         <v>15.75</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="23">
         <v>4.21</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="17">
         <v>10.78</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="24">
         <v>8.51</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="18">
         <v>9.52</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="15">
         <v>6.07</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="14">
         <v>2.19</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="19">
         <v>-8</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="20">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="16">
         <v>-12.72</v>
       </c>
-      <c r="T3" s="19">
-        <v>-48.19</v>
+      <c r="T3" s="21">
+        <v>-53.33</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>000856</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="28" t="str">
         <v>净卖: -799.12万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="30">
         <v>15.18</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="33">
         <v>26.73</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="39">
         <v>39.36</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="34">
         <v>53.27</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="35">
         <v>43.18</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="36">
         <v>29.45</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="31">
         <v>24.18</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="37">
         <v>23</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="27">
         <v>16.55</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="29">
         <v>16</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="38">
         <v>12</v>
       </c>
-      <c r="T4" s="39">
-        <v>-4.91</v>
+      <c r="T4" s="32">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="50">
         <v>16.27</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="42">
         <v>13.88</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="43">
         <v>14.94</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="44">
         <v>11.32</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="52">
         <v>7.25</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="51">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="40">
         <v>-8.4</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="47">
         <v>-11.23</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="46">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="48">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="50">
-        <v>-45.62</v>
+      <c r="T5" s="49">
+        <v>-51.02</v>
       </c>
     </row>
     <row r="6">
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>600881</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="65" t="str">
         <v>净卖: -413.93万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="58">
         <v>9.64</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="63">
         <v>13.71</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="56">
         <v>10.66</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="59">
         <v>7.11</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="53">
         <v>5.08</v>
       </c>
       <c r="N6" s="57">
         <v>6.09</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="54">
         <v>7.61</v>
       </c>
       <c r="P6" s="64">
         <v>3.55</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="60">
         <v>5.08</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="61">
         <v>4.06</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="62">
         <v>7.61</v>
       </c>
-      <c r="T6" s="62">
-        <v>-26.9</v>
+      <c r="T6" s="55">
+        <v>-24.87</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="75" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="76">
         <v>12.74</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="67">
         <v>35.28</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="77">
         <v>44.34</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="68">
         <v>37.24</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="78">
         <v>52.36</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="66">
         <v>52.32</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="69">
         <v>48.5</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="71">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="72">
         <v>66.56</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="70">
         <v>71.24</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="73">
         <v>61</v>
       </c>
-      <c r="T7" s="76">
-        <v>51.7</v>
+      <c r="T7" s="74">
+        <v>51.64</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>301488</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -1455.69万</v>
       </c>
       <c r="E8">
@@ -4493,41 +4493,41 @@
       <c r="H8">
         <v>8.31</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="80">
         <v>10.79</v>
       </c>
       <c r="J8" s="81">
         <v>18.2</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="82">
         <v>12.39</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="86">
         <v>24.77</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="89">
         <v>24.74</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="90">
         <v>21.61</v>
       </c>
       <c r="O8" s="83">
         <v>42.12</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="91">
         <v>36.4</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="84">
         <v>40.23</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="79">
         <v>31.84</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="87">
         <v>41.24</v>
       </c>
-      <c r="T8" s="86">
-        <v>24.23</v>
+      <c r="T8" s="88">
+        <v>24.18</v>
       </c>
     </row>
     <row r="9">
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.53</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="103">
         <v>7.31</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="99">
         <v>14.01</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="104">
         <v>11.84</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="100">
         <v>10.5</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="92">
         <v>4.53</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="93">
         <v>1.13</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="94">
         <v>3.09</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="97">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="98">
         <v>4.33</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="95">
         <v>3.3</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="101">
         <v>5.36</v>
       </c>
-      <c r="T9" s="100">
-        <v>-10.4</v>
+      <c r="T9" s="102">
+        <v>-12.56</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>603595</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="116" t="str">
         <v>净买: 1022.73万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="117">
         <v>6.97</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="107">
         <v>3.98</v>
       </c>
       <c r="K10" s="105">
         <v>-2.59</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="108">
         <v>-2.43</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="109">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="110">
         <v>-0.32</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="113">
         <v>3.94</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="111">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="112">
         <v>0.72</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="114">
         <v>-2.35</v>
       </c>
-      <c r="S10" s="112">
+      <c r="S10" s="115">
         <v>4.22</v>
       </c>
-      <c r="T10" s="111">
-        <v>-25.98</v>
+      <c r="T10" s="106">
+        <v>-26.81</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="128" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4679,31 +4679,31 @@
       <c r="H11">
         <v>10.19</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="121">
         <v>0</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="124">
         <v>10.08</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="119">
         <v>21.01</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="125">
         <v>25.63</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="126">
         <v>13.45</v>
       </c>
-      <c r="N11" s="129">
+      <c r="N11" s="122">
         <v>2.1</v>
       </c>
       <c r="O11" s="127">
         <v>-7.56</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="120">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="129">
         <v>-13.03</v>
       </c>
       <c r="R11" s="130">
@@ -4713,7 +4713,7 @@
         <v>-12.61</v>
       </c>
       <c r="T11" s="118">
-        <v>-26.89</v>
+        <v>-26.47</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002869</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="132" t="str">
         <v>净买: 798.76万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>0.31</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="141">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="136">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="142">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="140">
+      <c r="L12" s="133">
         <v>-11.67</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="139">
         <v>-12.05</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="143">
         <v>-11.84</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="137">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="134">
         <v>-14.8</v>
       </c>
-      <c r="Q12" s="142">
+      <c r="Q12" s="131">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="140">
         <v>-16.85</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="138">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="141">
-        <v>-26.29</v>
+      <c r="T12" s="135">
+        <v>-25.98</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>300827</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="153" t="str">
         <v>净卖: -1.68亿</v>
       </c>
       <c r="E13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="154">
         <v>19.01</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="147">
         <v>21.83</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="151">
         <v>18.48</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="148">
         <v>8.85</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="155">
         <v>8.24</v>
       </c>
       <c r="N13" s="149">
         <v>7.78</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="152">
         <v>0.85</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="156">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="145">
         <v>2</v>
       </c>
-      <c r="R13" s="150">
+      <c r="R13" s="146">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="153">
+      <c r="S13" s="144">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="146">
-        <v>-1.28</v>
+      <c r="T13" s="150">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="168" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="169">
         <v>3.51</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="161">
         <v>13.88</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="162">
         <v>25.25</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="157">
         <v>32.26</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="165">
         <v>32.76</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="158">
         <v>46.07</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="166">
         <v>51.79</v>
       </c>
       <c r="P14" s="160">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="163">
         <v>73.68</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="164">
         <v>56.29</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="159">
         <v>47.35</v>
       </c>
-      <c r="T14" s="163">
-        <v>47.5</v>
+      <c r="T14" s="167">
+        <v>41.49</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="170" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="175">
+      <c r="I15" s="173">
         <v>6.47</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="171">
         <v>2.54</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="181">
         <v>23.04</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="174">
         <v>12.25</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="178">
         <v>20.11</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="179">
         <v>7.01</v>
       </c>
-      <c r="O15" s="178">
+      <c r="O15" s="175">
         <v>5.08</v>
       </c>
       <c r="P15" s="180">
         <v>-0.31</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="176">
         <v>2.23</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="172">
         <v>1.77</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="177">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="174">
-        <v>-26.96</v>
+      <c r="T15" s="182">
+        <v>-26.5</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="188" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-2.65</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="195">
         <v>1.32</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="189">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="190">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="183">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="184">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="191">
         <v>-6.36</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="192">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="193">
         <v>-5.45</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="185">
         <v>-6.32</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="194">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="191">
+      <c r="S16" s="186">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="184">
-        <v>-9.88</v>
+      <c r="T16" s="187">
+        <v>-4.77</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="203" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="208">
         <v>0.04</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="196">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="197">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="204">
         <v>-2.98</v>
       </c>
-      <c r="M17" s="206">
+      <c r="M17" s="199">
         <v>-1.75</v>
       </c>
-      <c r="N17" s="207">
+      <c r="N17" s="206">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="200">
         <v>-0.79</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="201">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="198">
         <v>-2.22</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="205">
         <v>-2.14</v>
       </c>
-      <c r="S17" s="196">
+      <c r="S17" s="202">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="199">
-        <v>-5.44</v>
+      <c r="T17" s="207">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="18">
@@ -5147,16 +5147,16 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="216">
+      <c r="I19" s="218">
         <v>87.5</v>
       </c>
-      <c r="J19" s="217">
+      <c r="J19" s="219">
         <v>81.25</v>
       </c>
-      <c r="K19" s="210">
+      <c r="K19" s="220">
         <v>75</v>
       </c>
-      <c r="L19" s="211">
+      <c r="L19" s="214">
         <v>75</v>
       </c>
       <c r="M19" s="212">
@@ -5165,22 +5165,22 @@
       <c r="N19" s="213">
         <v>68.75</v>
       </c>
-      <c r="O19" s="219">
+      <c r="O19" s="209">
         <v>68.75</v>
       </c>
-      <c r="P19" s="218">
+      <c r="P19" s="216">
         <v>62.5</v>
       </c>
-      <c r="Q19" s="214">
+      <c r="Q19" s="210">
         <v>62.5</v>
       </c>
-      <c r="R19" s="220">
+      <c r="R19" s="215">
         <v>50</v>
       </c>
-      <c r="S19" s="215">
+      <c r="S19" s="211">
         <v>50</v>
       </c>
-      <c r="T19" s="209">
+      <c r="T19" s="217">
         <v>18.75</v>
       </c>
     </row>
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="228">
+      <c r="I20" s="224">
         <v>7.43</v>
       </c>
-      <c r="J20" s="223">
+      <c r="J20" s="228">
         <v>12.45</v>
       </c>
       <c r="K20" s="221">
         <v>15.15</v>
       </c>
-      <c r="L20" s="224">
+      <c r="L20" s="222">
         <v>14.59</v>
       </c>
-      <c r="M20" s="229">
+      <c r="M20" s="223">
         <v>14.15</v>
       </c>
-      <c r="N20" s="225">
+      <c r="N20" s="230">
         <v>11.63</v>
       </c>
-      <c r="O20" s="230">
+      <c r="O20" s="225">
         <v>11.45</v>
       </c>
-      <c r="P20" s="231">
+      <c r="P20" s="229">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="222">
+      <c r="Q20" s="226">
         <v>10.79</v>
       </c>
-      <c r="R20" s="226">
+      <c r="R20" s="231">
         <v>7.69</v>
       </c>
-      <c r="S20" s="227">
+      <c r="S20" s="232">
         <v>6.9</v>
       </c>
-      <c r="T20" s="232">
-        <v>-10.88</v>
+      <c r="T20" s="227">
+        <v>-11.54</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/乔帮主/index.xlsx
+++ b/youzi/乔帮主/index.xlsx
@@ -39,12 +39,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE9828C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -57,43 +123,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,7 +159,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB62432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,31 +171,559 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,30 +735,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -201,79 +783,241 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,7 +1047,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,1087 +1089,313 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4124,38 +4124,38 @@
       <c r="I2" s="4">
         <v>13.05</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="13">
         <v>24.4</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="11">
         <v>36.85</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="1">
         <v>23.21</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="9">
         <v>30.98</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="12">
         <v>28.29</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="10">
         <v>29.48</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="5">
         <v>25.4</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="6">
         <v>20.82</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="2">
         <v>8.76</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="7">
         <v>3.09</v>
       </c>
-      <c r="T2" s="11">
-        <v>-44.82</v>
+      <c r="T2" s="8">
+        <v>-42.73</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>002691</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="14" t="str">
         <v>净卖: -1625.65万</v>
       </c>
       <c r="E3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>4.58</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="15">
         <v>5.22</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="20">
         <v>15.75</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="16">
         <v>4.21</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="24">
         <v>10.78</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="21">
         <v>8.51</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="17">
         <v>9.52</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="18">
         <v>6.07</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="22">
         <v>2.19</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="23">
         <v>-8</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="25">
         <v>-12.81</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="19">
         <v>-12.72</v>
       </c>
-      <c r="T3" s="21">
-        <v>-53.33</v>
+      <c r="T3" s="26">
+        <v>-51.56</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>000856</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -799.12万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-4.51</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>15.18</v>
       </c>
       <c r="J4" s="33">
         <v>26.73</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="37">
         <v>39.36</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="38">
         <v>53.27</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="29">
         <v>43.18</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="39">
         <v>29.45</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="27">
         <v>24.18</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="34">
         <v>23</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="28">
         <v>16.55</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="32">
         <v>16</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="35">
         <v>12</v>
       </c>
-      <c r="T4" s="32">
-        <v>-3.09</v>
+      <c r="T4" s="36">
+        <v>-12.82</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002691</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -871.83万</v>
       </c>
       <c r="E5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>-8.57</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="43">
         <v>16.27</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="41">
         <v>13.88</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="52">
         <v>14.94</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="42">
         <v>11.32</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="40">
         <v>7.25</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="49">
         <v>-3.45</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="44">
         <v>-8.49</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="45">
         <v>-8.4</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="50">
         <v>-11.23</v>
       </c>
       <c r="R5" s="46">
         <v>-14.41</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="47">
         <v>-15.21</v>
       </c>
-      <c r="T5" s="49">
-        <v>-51.02</v>
+      <c r="T5" s="48">
+        <v>-49.16</v>
       </c>
     </row>
     <row r="6">
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>600881</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="61" t="str">
         <v>净卖: -413.93万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>0.51</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="54">
         <v>9.64</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="57">
         <v>13.71</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="62">
         <v>10.66</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="63">
         <v>7.11</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="58">
         <v>5.08</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="59">
         <v>6.09</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="60">
         <v>7.61</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="55">
         <v>3.55</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="64">
         <v>5.08</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="65">
         <v>4.06</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="53">
         <v>7.61</v>
       </c>
-      <c r="T6" s="55">
-        <v>-24.87</v>
+      <c r="T6" s="56">
+        <v>-26.9</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>301488</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="78" t="str">
         <v>净卖: -1456.47万</v>
       </c>
       <c r="E7">
@@ -4431,31 +4431,31 @@
       <c r="H7">
         <v>6.44</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="71">
         <v>12.74</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="66">
         <v>35.28</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="67">
         <v>44.34</v>
       </c>
       <c r="L7" s="68">
         <v>37.24</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="69">
         <v>52.36</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="72">
         <v>52.32</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="75">
         <v>48.5</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="76">
         <v>73.55</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="77">
         <v>66.56</v>
       </c>
       <c r="R7" s="70">
@@ -4465,7 +4465,7 @@
         <v>61</v>
       </c>
       <c r="T7" s="74">
-        <v>51.64</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>301488</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -1455.69万</v>
       </c>
       <c r="E8">
@@ -4493,41 +4493,41 @@
       <c r="H8">
         <v>8.31</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="79">
         <v>10.79</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="87">
         <v>18.2</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="80">
         <v>12.39</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="88">
         <v>24.77</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="81">
         <v>24.74</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="82">
         <v>21.61</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="89">
         <v>42.12</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="83">
         <v>36.4</v>
       </c>
       <c r="Q8" s="84">
         <v>40.23</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="90">
         <v>31.84</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="85">
         <v>41.24</v>
       </c>
-      <c r="T8" s="88">
-        <v>24.18</v>
+      <c r="T8" s="86">
+        <v>17.71</v>
       </c>
     </row>
     <row r="9">
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>600721</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -656.16万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.53</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="104">
         <v>7.31</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="98">
         <v>14.01</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="94">
         <v>11.84</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="95">
         <v>10.5</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="99">
         <v>4.53</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="100">
         <v>1.13</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="101">
         <v>3.09</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="92">
         <v>4.43</v>
       </c>
-      <c r="Q9" s="98">
+      <c r="Q9" s="93">
         <v>4.33</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="102">
         <v>3.3</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="96">
         <v>5.36</v>
       </c>
-      <c r="T9" s="102">
-        <v>-12.56</v>
+      <c r="T9" s="103">
+        <v>-13.18</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>603595</v>
       </c>
-      <c r="D10" s="116" t="str">
+      <c r="D10" s="109" t="str">
         <v>净买: 1022.73万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>-3.39</v>
       </c>
-      <c r="I10" s="117">
+      <c r="I10" s="110">
         <v>6.97</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="117">
         <v>3.98</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="111">
         <v>-2.59</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="112">
         <v>-2.43</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="107">
         <v>-3.47</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="108">
         <v>-0.32</v>
       </c>
       <c r="O10" s="113">
         <v>3.94</v>
       </c>
-      <c r="P10" s="111">
+      <c r="P10" s="105">
         <v>2.07</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="114">
         <v>0.72</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="106">
         <v>-2.35</v>
       </c>
       <c r="S10" s="115">
         <v>4.22</v>
       </c>
-      <c r="T10" s="106">
-        <v>-26.81</v>
+      <c r="T10" s="116">
+        <v>-26.61</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>600162</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -314.04万</v>
       </c>
       <c r="E11">
@@ -4679,41 +4679,41 @@
       <c r="H11">
         <v>10.19</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="130">
         <v>0</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="123">
         <v>10.08</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="124">
         <v>21.01</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="118">
         <v>25.63</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="119">
         <v>13.45</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="120">
         <v>2.1</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="125">
         <v>-7.56</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="127">
         <v>-9.66</v>
       </c>
-      <c r="Q11" s="129">
+      <c r="Q11" s="121">
         <v>-13.03</v>
       </c>
-      <c r="R11" s="130">
+      <c r="R11" s="126">
         <v>-11.34</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="128">
         <v>-12.61</v>
       </c>
-      <c r="T11" s="118">
-        <v>-26.47</v>
+      <c r="T11" s="129">
+        <v>-27.31</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002869</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="140" t="str">
         <v>净买: 798.76万</v>
       </c>
       <c r="E12">
@@ -4744,38 +4744,38 @@
       <c r="I12" s="141">
         <v>-8.72</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="137">
         <v>-8.54</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="132">
         <v>-8.86</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="138">
         <v>-11.67</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="135">
         <v>-12.05</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="142">
         <v>-11.84</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="133">
         <v>-14.83</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="143">
         <v>-14.8</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="134">
         <v>-18.79</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="139">
         <v>-16.85</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="131">
         <v>-15.53</v>
       </c>
-      <c r="T12" s="135">
-        <v>-25.98</v>
+      <c r="T12" s="136">
+        <v>-25.43</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>300827</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="155" t="str">
         <v>净卖: -1.68亿</v>
       </c>
       <c r="E13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>0.83</v>
       </c>
-      <c r="I13" s="154">
+      <c r="I13" s="145">
         <v>19.01</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="150">
         <v>21.83</v>
       </c>
-      <c r="K13" s="151">
+      <c r="K13" s="147">
         <v>18.48</v>
       </c>
       <c r="L13" s="148">
         <v>8.85</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="151">
         <v>8.24</v>
       </c>
-      <c r="N13" s="149">
+      <c r="N13" s="156">
         <v>7.78</v>
       </c>
       <c r="O13" s="152">
         <v>0.85</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="146">
         <v>0.19</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="149">
         <v>2</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="153">
         <v>-3.47</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="154">
         <v>-2.96</v>
       </c>
-      <c r="T13" s="150">
-        <v>-1.57</v>
+      <c r="T13" s="144">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>002703</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="165" t="str">
         <v>净卖: -2404.90万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>6.31</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="159">
         <v>3.51</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="169">
         <v>13.88</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="160">
         <v>25.25</v>
       </c>
-      <c r="L14" s="157">
+      <c r="L14" s="161">
         <v>32.26</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="166">
         <v>32.76</v>
       </c>
-      <c r="N14" s="158">
+      <c r="N14" s="157">
         <v>46.07</v>
       </c>
-      <c r="O14" s="166">
+      <c r="O14" s="164">
         <v>51.79</v>
       </c>
-      <c r="P14" s="160">
+      <c r="P14" s="167">
         <v>66.95</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="162">
         <v>73.68</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="163">
         <v>56.29</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="168">
         <v>47.35</v>
       </c>
-      <c r="T14" s="167">
-        <v>41.49</v>
+      <c r="T14" s="158">
+        <v>27.32</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>300887</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="176" t="str">
         <v>净卖: -583.39万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>12.67</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="177">
         <v>6.47</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="178">
         <v>2.54</v>
       </c>
-      <c r="K15" s="181">
+      <c r="K15" s="179">
         <v>23.04</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="182">
         <v>12.25</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="180">
         <v>20.11</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="173">
         <v>7.01</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="170">
         <v>5.08</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="174">
         <v>-0.31</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="181">
         <v>2.23</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="171">
         <v>1.77</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="172">
         <v>-3.78</v>
       </c>
-      <c r="T15" s="182">
-        <v>-26.5</v>
+      <c r="T15" s="175">
+        <v>-28.97</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>001231</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="195" t="str">
         <v>净买: 453.42万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-2.65</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="185">
         <v>1.32</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="192">
         <v>-4.65</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="186">
         <v>-6.43</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="184">
         <v>-6.62</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="187">
         <v>-7.53</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="188">
         <v>-6.36</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="193">
         <v>-7.87</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="189">
         <v>-5.45</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="190">
         <v>-6.32</v>
       </c>
       <c r="R16" s="194">
         <v>-6.81</v>
       </c>
-      <c r="S16" s="186">
+      <c r="S16" s="183">
         <v>-6.73</v>
       </c>
-      <c r="T16" s="187">
-        <v>-4.77</v>
+      <c r="T16" s="191">
+        <v>-4.69</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>001231</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="206" t="str">
         <v>净卖: -347.06万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>-5.94</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="198">
         <v>0.04</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="208">
         <v>-1.83</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="205">
         <v>-2.02</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="207">
         <v>-2.98</v>
       </c>
       <c r="M17" s="199">
         <v>-1.75</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="200">
         <v>-3.33</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="196">
         <v>-0.79</v>
       </c>
       <c r="P17" s="201">
         <v>-1.71</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="197">
         <v>-2.22</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="202">
         <v>-2.14</v>
       </c>
-      <c r="S17" s="202">
+      <c r="S17" s="203">
         <v>-1.87</v>
       </c>
-      <c r="T17" s="207">
-        <v>-0.08</v>
+      <c r="T17" s="204">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="218">
+      <c r="I19" s="216">
         <v>87.5</v>
       </c>
-      <c r="J19" s="219">
+      <c r="J19" s="217">
         <v>81.25</v>
       </c>
-      <c r="K19" s="220">
+      <c r="K19" s="215">
         <v>75</v>
       </c>
-      <c r="L19" s="214">
+      <c r="L19" s="209">
         <v>75</v>
       </c>
-      <c r="M19" s="212">
+      <c r="M19" s="218">
         <v>75</v>
       </c>
-      <c r="N19" s="213">
+      <c r="N19" s="210">
         <v>68.75</v>
       </c>
-      <c r="O19" s="209">
+      <c r="O19" s="211">
         <v>68.75</v>
       </c>
-      <c r="P19" s="216">
+      <c r="P19" s="212">
         <v>62.5</v>
       </c>
-      <c r="Q19" s="210">
+      <c r="Q19" s="219">
         <v>62.5</v>
       </c>
-      <c r="R19" s="215">
+      <c r="R19" s="220">
         <v>50</v>
       </c>
-      <c r="S19" s="211">
+      <c r="S19" s="213">
         <v>50</v>
       </c>
-      <c r="T19" s="217">
+      <c r="T19" s="214">
         <v>18.75</v>
       </c>
     </row>
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="224">
+      <c r="I20" s="232">
         <v>7.43</v>
       </c>
-      <c r="J20" s="228">
+      <c r="J20" s="229">
         <v>12.45</v>
       </c>
-      <c r="K20" s="221">
+      <c r="K20" s="225">
         <v>15.15</v>
       </c>
-      <c r="L20" s="222">
+      <c r="L20" s="231">
         <v>14.59</v>
       </c>
-      <c r="M20" s="223">
+      <c r="M20" s="221">
         <v>14.15</v>
       </c>
-      <c r="N20" s="230">
+      <c r="N20" s="222">
         <v>11.63</v>
       </c>
-      <c r="O20" s="225">
+      <c r="O20" s="223">
         <v>11.45</v>
       </c>
-      <c r="P20" s="229">
+      <c r="P20" s="226">
         <v>12.34</v>
       </c>
-      <c r="Q20" s="226">
+      <c r="Q20" s="227">
         <v>10.79</v>
       </c>
-      <c r="R20" s="231">
+      <c r="R20" s="230">
         <v>7.69</v>
       </c>
-      <c r="S20" s="232">
+      <c r="S20" s="228">
         <v>6.9</v>
       </c>
-      <c r="T20" s="227">
-        <v>-11.54</v>
+      <c r="T20" s="224">
+        <v>-14</v>
       </c>
     </row>
   </sheetData>
